--- a/historico_rateios.xlsx
+++ b/historico_rateios.xlsx
@@ -47,8 +47,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,6 +485,303 @@
       <c r="G2" t="inlineStr">
         <is>
           <t>PARCIAL (1 falhas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>09/04/2025 13:29:44</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>05/04/2025</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>testando</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>150</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>09/04/2025 16:06:42</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>20/04/2025</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>testando dados</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>235</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>09/04/2025 17:59:58</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>05/04/2025</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ref. 03/2025</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>970</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>09/04/2025 18:03:41</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>05/04/2025</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ref.: 03/2025</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>140</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>PARCIAL (1 falhas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>09/04/2025 18:23:00</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>20/04/2025</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>teste 'lançamento automático'</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>140</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>09/04/2025 18:45:52</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>20/04/2025</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>teste janela</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>100</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>09/04/2025 18:50:18</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>20/04/2025</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>testando</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>253</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>09/04/2025 18:53:17</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>20/04/2025</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TESTE HISTÓRICO</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>156</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10/04/2025 16:14:22</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>05/04/2025</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>COMPETENCIA 03/2025</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>4554</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
         </is>
       </c>
     </row>
@@ -498,7 +796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,6 +839,240 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BRUNO SANTANA RINALDI</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>150</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BRUNO SANTANA RINALDI</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>235</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BRUNO SANTANA RINALDI</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>970</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BRUNO SANTANA RINALDI</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>140</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FALHA: string indices must be integers, not 'str'</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BRUNO SANTANA RINALDI</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>140</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BRUNO SANTANA RINALDI</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>100</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BRUNO SANTANA RINALDI</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>253</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BRUNO SANTANA RINALDI</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>156</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CLEVER LUIZ SALVADOR</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>910.8000000000001</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GILMAR ALMEIDA PORTUGAL</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>910.8000000000001</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>JOSÉ PAULO DE SOUZA PEIXE</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>910.8000000000001</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>RHAUFED RODRIGUES DOS SANTOS</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>910.8000000000001</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>RONALDO ROLIM DE OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>910.8000000000001</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/historico_rateios.xlsx
+++ b/historico_rateios.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,6 +780,72 @@
         <v>5</v>
       </c>
       <c r="G11" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>28/04/2025 16:06:06</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>05/05/2025</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ref. 03/2025</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>584</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>28/04/2025 16:43:57</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>05/05/2025</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ref. 04/2025</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>SUCESSO</t>
         </is>
@@ -796,7 +862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1073,6 +1139,114 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BRUNO SANTANA RINALDI</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>EDIGAR BATISTA FERREIRA</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>FERNANDO HENRIQUE FARIA BARBASSA</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>11</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>SERGIO LUCIO PEREIRA</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>12</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BRUNO SANTANA RINALDI</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SERGIO LUCIO PEREIRA</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SUCESSO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
